--- a/2022 data/excel_outputs/78_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/78_boothwise_data.xlsx
@@ -14,11 +14,92 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="547">
   <si>
     <t>AC 78 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
+    <t>Unnamed: 24</t>
+  </si>
+  <si>
+    <t>Unnamed: 25</t>
+  </si>
+  <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
+    <t>Unnamed: 27</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -226,7 +307,7 @@
     <t>P. S. NAGLA PAUPA</t>
   </si>
   <si>
-    <t>####0 ####0 #########</t>
+    <t>PRA0PA0 BHAUJAG.DHI</t>
   </si>
   <si>
     <t>COMPOSIT S. NAGALA THAKUR</t>
@@ -1580,8 +1661,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1597,7 +1686,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1605,12 +1694,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1909,94 +2016,175 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:28">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:28">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>495</v>
+        <v>522</v>
       </c>
       <c r="D2" t="s">
-        <v>496</v>
+        <v>523</v>
       </c>
       <c r="E2" t="s">
-        <v>497</v>
+        <v>524</v>
       </c>
       <c r="F2" t="s">
-        <v>498</v>
+        <v>525</v>
       </c>
       <c r="G2" t="s">
-        <v>499</v>
+        <v>526</v>
       </c>
       <c r="H2" t="s">
-        <v>500</v>
+        <v>527</v>
       </c>
       <c r="I2" t="s">
-        <v>501</v>
+        <v>528</v>
       </c>
       <c r="J2" t="s">
-        <v>502</v>
+        <v>529</v>
       </c>
       <c r="K2" t="s">
-        <v>503</v>
+        <v>530</v>
       </c>
       <c r="L2" t="s">
-        <v>504</v>
+        <v>531</v>
       </c>
       <c r="M2" t="s">
-        <v>505</v>
+        <v>532</v>
       </c>
       <c r="N2" t="s">
-        <v>506</v>
+        <v>533</v>
       </c>
       <c r="O2" t="s">
-        <v>507</v>
+        <v>534</v>
       </c>
       <c r="P2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="Q2" t="s">
-        <v>509</v>
+        <v>536</v>
       </c>
       <c r="R2" t="s">
-        <v>510</v>
+        <v>537</v>
       </c>
       <c r="S2" t="s">
-        <v>511</v>
+        <v>538</v>
       </c>
       <c r="T2" t="s">
-        <v>512</v>
+        <v>539</v>
       </c>
       <c r="U2" t="s">
-        <v>513</v>
+        <v>540</v>
       </c>
       <c r="V2" t="s">
-        <v>514</v>
+        <v>541</v>
       </c>
       <c r="W2" t="s">
-        <v>515</v>
+        <v>542</v>
       </c>
       <c r="X2" t="s">
-        <v>516</v>
+        <v>543</v>
       </c>
       <c r="Y2" t="s">
-        <v>517</v>
+        <v>544</v>
       </c>
       <c r="Z2" t="s">
-        <v>517</v>
+        <v>544</v>
       </c>
       <c r="AA2" t="s">
-        <v>518</v>
+        <v>545</v>
       </c>
       <c r="AB2" t="s">
-        <v>519</v>
+        <v>546</v>
       </c>
     </row>
     <row r="3" spans="1:28">
@@ -2004,7 +2192,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C3">
         <v>1096</v>
@@ -2090,7 +2278,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C4">
         <v>735</v>
@@ -2176,7 +2364,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="C5">
         <v>726</v>
@@ -2262,7 +2450,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="C6">
         <v>315</v>
@@ -2348,7 +2536,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="C7">
         <v>825</v>
@@ -2434,7 +2622,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="C8">
         <v>1004</v>
@@ -2520,7 +2708,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="C9">
         <v>724</v>
@@ -2606,7 +2794,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="C10">
         <v>716</v>
@@ -2692,7 +2880,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="C11">
         <v>916</v>
@@ -2778,7 +2966,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C12">
         <v>1118</v>
@@ -2864,7 +3052,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="C13">
         <v>806</v>
@@ -2950,7 +3138,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="C14">
         <v>1216</v>
@@ -3036,7 +3224,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="C15">
         <v>528</v>
@@ -3122,7 +3310,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="C16">
         <v>1227</v>
@@ -3208,7 +3396,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="C17">
         <v>703</v>
@@ -3294,7 +3482,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="C18">
         <v>899</v>
@@ -3380,7 +3568,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="C19">
         <v>826</v>
@@ -3466,7 +3654,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="C20">
         <v>759</v>
@@ -3552,7 +3740,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="C21">
         <v>1233</v>
@@ -3638,7 +3826,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="C22">
         <v>573</v>
@@ -3724,7 +3912,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="C23">
         <v>507</v>
@@ -3810,7 +3998,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="C24">
         <v>684</v>
@@ -3896,7 +4084,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="C25">
         <v>702</v>
@@ -3982,7 +4170,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="C26">
         <v>990</v>
@@ -4068,7 +4256,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="C27">
         <v>1178</v>
@@ -4154,7 +4342,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="C28">
         <v>1222</v>
@@ -4240,7 +4428,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="C29">
         <v>1096</v>
@@ -4326,7 +4514,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="C30">
         <v>682</v>
@@ -4412,7 +4600,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="C31">
         <v>810</v>
@@ -4498,7 +4686,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="C32">
         <v>717</v>
@@ -4584,7 +4772,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="C33">
         <v>520</v>
@@ -4670,7 +4858,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C34">
         <v>1045</v>
@@ -4756,7 +4944,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="C35">
         <v>1060</v>
@@ -4842,7 +5030,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="C36">
         <v>630</v>
@@ -4928,7 +5116,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="C37">
         <v>1107</v>
@@ -5014,7 +5202,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="C38">
         <v>840</v>
@@ -5100,7 +5288,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="C39">
         <v>730</v>
@@ -5186,7 +5374,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="C40">
         <v>614</v>
@@ -5272,7 +5460,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C41">
         <v>1004</v>
@@ -5358,7 +5546,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="C42">
         <v>885</v>
@@ -5444,7 +5632,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="C43">
         <v>750</v>
@@ -5530,7 +5718,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="C44">
         <v>711</v>
@@ -5616,7 +5804,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="C45">
         <v>686</v>
@@ -5702,7 +5890,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="C46">
         <v>890</v>
@@ -5788,7 +5976,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="C47">
         <v>587</v>
@@ -5874,7 +6062,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="C48">
         <v>1159</v>
@@ -5960,7 +6148,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="C49">
         <v>1097</v>
@@ -6046,7 +6234,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="C50">
         <v>1049</v>
@@ -6132,7 +6320,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="C51">
         <v>793</v>
@@ -6218,7 +6406,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="C52">
         <v>949</v>
@@ -6304,7 +6492,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="C53">
         <v>906</v>
@@ -6390,7 +6578,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="C54">
         <v>1119</v>
@@ -6476,7 +6664,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="C55">
         <v>971</v>
@@ -6562,7 +6750,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="C56">
         <v>758</v>
@@ -6648,7 +6836,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="C57">
         <v>656</v>
@@ -6734,7 +6922,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="C58">
         <v>686</v>
@@ -6820,7 +7008,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="C59">
         <v>602</v>
@@ -6906,7 +7094,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="C60">
         <v>593</v>
@@ -6992,7 +7180,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="C61">
         <v>805</v>
@@ -7078,7 +7266,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="C62">
         <v>815</v>
@@ -7164,7 +7352,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="C63">
         <v>793</v>
@@ -7250,7 +7438,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="C64">
         <v>765</v>
@@ -7336,7 +7524,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="C65">
         <v>401</v>
@@ -7422,7 +7610,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="C66">
         <v>543</v>
@@ -7508,7 +7696,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="C67">
         <v>975</v>
@@ -7594,7 +7782,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="C68">
         <v>989</v>
@@ -7680,7 +7868,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="C69">
         <v>1049</v>
@@ -7766,7 +7954,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="C70">
         <v>427</v>
@@ -7852,7 +8040,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="C71">
         <v>307</v>
@@ -7938,7 +8126,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="C72">
         <v>1204</v>
@@ -8024,7 +8212,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="C73">
         <v>914</v>
@@ -8110,7 +8298,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="C74">
         <v>1007</v>
@@ -8196,7 +8384,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="C75">
         <v>752</v>
@@ -8282,7 +8470,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="C76">
         <v>680</v>
@@ -8368,7 +8556,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="C77">
         <v>990</v>
@@ -8454,7 +8642,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="C78">
         <v>1089</v>
@@ -8540,7 +8728,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="C79">
         <v>832</v>
@@ -8626,7 +8814,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="C80">
         <v>1010</v>
@@ -8712,7 +8900,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="C81">
         <v>924</v>
@@ -8798,7 +8986,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="C82">
         <v>778</v>
@@ -8884,7 +9072,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="C83">
         <v>1158</v>
@@ -8970,7 +9158,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="C84">
         <v>928</v>
@@ -9056,7 +9244,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="C85">
         <v>994</v>
@@ -9142,7 +9330,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C86">
         <v>542</v>
@@ -9228,7 +9416,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="C87">
         <v>857</v>
@@ -9314,7 +9502,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="C88">
         <v>854</v>
@@ -9400,7 +9588,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="C89">
         <v>819</v>
@@ -9486,7 +9674,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="C90">
         <v>797</v>
@@ -9572,7 +9760,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="C91">
         <v>776</v>
@@ -9658,7 +9846,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="C92">
         <v>603</v>
@@ -9744,7 +9932,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="C93">
         <v>978</v>
@@ -9830,7 +10018,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="C94">
         <v>1166</v>
@@ -9916,7 +10104,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="C95">
         <v>693</v>
@@ -10002,7 +10190,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="C96">
         <v>971</v>
@@ -10088,7 +10276,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="C97">
         <v>922</v>
@@ -10174,7 +10362,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="C98">
         <v>1038</v>
@@ -10260,7 +10448,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="C99">
         <v>1115</v>
@@ -10346,7 +10534,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="C100">
         <v>961</v>
@@ -10432,7 +10620,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="C101">
         <v>1087</v>
@@ -10518,7 +10706,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="C102">
         <v>1042</v>
@@ -10604,7 +10792,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="C103">
         <v>960</v>
@@ -10690,7 +10878,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="C104">
         <v>1021</v>
@@ -10776,7 +10964,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="C105">
         <v>885</v>
@@ -10862,7 +11050,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="C106">
         <v>897</v>
@@ -10948,7 +11136,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="C107">
         <v>818</v>
@@ -11034,7 +11222,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="C108">
         <v>743</v>
@@ -11120,7 +11308,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="C109">
         <v>447</v>
@@ -11206,7 +11394,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="C110">
         <v>1018</v>
@@ -11292,7 +11480,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="C111">
         <v>445</v>
@@ -11378,7 +11566,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="C112">
         <v>1213</v>
@@ -11464,7 +11652,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="C113">
         <v>668</v>
@@ -11550,7 +11738,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="C114">
         <v>948</v>
@@ -11636,7 +11824,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="C115">
         <v>922</v>
@@ -11722,7 +11910,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="C116">
         <v>985</v>
@@ -11808,7 +11996,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="C117">
         <v>991</v>
@@ -11894,7 +12082,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="C118">
         <v>715</v>
@@ -11980,7 +12168,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="C119">
         <v>460</v>
@@ -12066,7 +12254,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="C120">
         <v>863</v>
@@ -12152,7 +12340,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="C121">
         <v>743</v>
@@ -12238,7 +12426,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="C122">
         <v>1039</v>
@@ -12324,7 +12512,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="C123">
         <v>698</v>
@@ -12410,7 +12598,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="C124">
         <v>704</v>
@@ -12496,7 +12684,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="C125">
         <v>556</v>
@@ -12582,7 +12770,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="C126">
         <v>809</v>
@@ -12668,7 +12856,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="C127">
         <v>482</v>
@@ -12754,7 +12942,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="C128">
         <v>932</v>
@@ -12840,7 +13028,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="C129">
         <v>488</v>
@@ -12926,7 +13114,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="C130">
         <v>1067</v>
@@ -13012,7 +13200,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="C131">
         <v>931</v>
@@ -13098,7 +13286,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="C132">
         <v>912</v>
@@ -13184,7 +13372,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="C133">
         <v>1221</v>
@@ -13270,7 +13458,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="C134">
         <v>1136</v>
@@ -13356,7 +13544,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="C135">
         <v>1083</v>
@@ -13442,7 +13630,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="C136">
         <v>418</v>
@@ -13528,7 +13716,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>137</v>
+        <v>164</v>
       </c>
       <c r="C137">
         <v>613</v>
@@ -13614,7 +13802,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="C138">
         <v>941</v>
@@ -13700,7 +13888,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="C139">
         <v>901</v>
@@ -13786,7 +13974,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="C140">
         <v>1109</v>
@@ -13872,7 +14060,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="C141">
         <v>1032</v>
@@ -13958,7 +14146,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="C142">
         <v>610</v>
@@ -14044,7 +14232,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="C143">
         <v>626</v>
@@ -14130,7 +14318,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="C144">
         <v>912</v>
@@ -14216,7 +14404,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="C145">
         <v>521</v>
@@ -14302,7 +14490,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="C146">
         <v>1147</v>
@@ -14388,7 +14576,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="C147">
         <v>868</v>
@@ -14474,7 +14662,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="C148">
         <v>1086</v>
@@ -14560,7 +14748,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>149</v>
+        <v>176</v>
       </c>
       <c r="C149">
         <v>1167</v>
@@ -14646,7 +14834,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="C150">
         <v>1220</v>
@@ -14732,7 +14920,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="C151">
         <v>1013</v>
@@ -14818,7 +15006,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="C152">
         <v>1112</v>
@@ -14904,7 +15092,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="C153">
         <v>754</v>
@@ -14990,7 +15178,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="C154">
         <v>1135</v>
@@ -15076,7 +15264,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="C155">
         <v>739</v>
@@ -15162,7 +15350,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="C156">
         <v>997</v>
@@ -15248,7 +15436,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="C157">
         <v>1143</v>
@@ -15334,7 +15522,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>158</v>
+        <v>185</v>
       </c>
       <c r="C158">
         <v>911</v>
@@ -15420,7 +15608,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="C159">
         <v>1041</v>
@@ -15506,7 +15694,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>160</v>
+        <v>187</v>
       </c>
       <c r="C160">
         <v>676</v>
@@ -15592,7 +15780,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="C161">
         <v>831</v>
@@ -15678,7 +15866,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="C162">
         <v>1066</v>
@@ -15764,7 +15952,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="C163">
         <v>1152</v>
@@ -15850,7 +16038,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="C164">
         <v>980</v>
@@ -15936,7 +16124,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="C165">
         <v>747</v>
@@ -16022,7 +16210,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="C166">
         <v>676</v>
@@ -16108,7 +16296,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="C167">
         <v>511</v>
@@ -16194,7 +16382,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="C168">
         <v>1001</v>
@@ -16280,7 +16468,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="C169">
         <v>628</v>
@@ -16366,7 +16554,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="C170">
         <v>908</v>
@@ -16452,7 +16640,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="C171">
         <v>905</v>
@@ -16538,7 +16726,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="C172">
         <v>775</v>
@@ -16624,7 +16812,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="C173">
         <v>687</v>
@@ -16710,7 +16898,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="C174">
         <v>1210</v>
@@ -16796,7 +16984,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="C175">
         <v>995</v>
@@ -16882,7 +17070,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="C176">
         <v>480</v>
@@ -16968,7 +17156,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="C177">
         <v>703</v>
@@ -17054,7 +17242,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="C178">
         <v>668</v>
@@ -17140,7 +17328,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="C179">
         <v>943</v>
@@ -17226,7 +17414,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="C180">
         <v>365</v>
@@ -17312,7 +17500,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>181</v>
+        <v>208</v>
       </c>
       <c r="C181">
         <v>731</v>
@@ -17398,7 +17586,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="C182">
         <v>438</v>
@@ -17484,7 +17672,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="C183">
         <v>852</v>
@@ -17570,7 +17758,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="C184">
         <v>682</v>
@@ -17656,7 +17844,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="C185">
         <v>665</v>
@@ -17742,7 +17930,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>186</v>
+        <v>213</v>
       </c>
       <c r="C186">
         <v>687</v>
@@ -17828,7 +18016,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="C187">
         <v>702</v>
@@ -17914,7 +18102,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="C188">
         <v>845</v>
@@ -18000,7 +18188,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="C189">
         <v>305</v>
@@ -18086,7 +18274,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>190</v>
+        <v>217</v>
       </c>
       <c r="C190">
         <v>1046</v>
@@ -18172,7 +18360,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>191</v>
+        <v>218</v>
       </c>
       <c r="C191">
         <v>929</v>
@@ -18258,7 +18446,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>192</v>
+        <v>219</v>
       </c>
       <c r="C192">
         <v>582</v>
@@ -18344,7 +18532,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>193</v>
+        <v>220</v>
       </c>
       <c r="C193">
         <v>1149</v>
@@ -18430,7 +18618,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>194</v>
+        <v>221</v>
       </c>
       <c r="C194">
         <v>860</v>
@@ -18516,7 +18704,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="C195">
         <v>539</v>
@@ -18602,7 +18790,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>196</v>
+        <v>223</v>
       </c>
       <c r="C196">
         <v>1163</v>
@@ -18688,7 +18876,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="C197">
         <v>684</v>
@@ -18774,7 +18962,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>198</v>
+        <v>225</v>
       </c>
       <c r="C198">
         <v>798</v>
@@ -18860,7 +19048,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>199</v>
+        <v>226</v>
       </c>
       <c r="C199">
         <v>999</v>
@@ -18946,7 +19134,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>200</v>
+        <v>227</v>
       </c>
       <c r="C200">
         <v>881</v>
@@ -19032,7 +19220,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>201</v>
+        <v>228</v>
       </c>
       <c r="C201">
         <v>879</v>
@@ -19118,7 +19306,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="C202">
         <v>683</v>
@@ -19204,7 +19392,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="C203">
         <v>1073</v>
@@ -19290,7 +19478,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="C204">
         <v>927</v>
@@ -19376,7 +19564,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>205</v>
+        <v>232</v>
       </c>
       <c r="C205">
         <v>722</v>
@@ -19462,7 +19650,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>206</v>
+        <v>233</v>
       </c>
       <c r="C206">
         <v>456</v>
@@ -19548,7 +19736,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>207</v>
+        <v>234</v>
       </c>
       <c r="C207">
         <v>1172</v>
@@ -19634,7 +19822,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>208</v>
+        <v>235</v>
       </c>
       <c r="C208">
         <v>1152</v>
@@ -19720,7 +19908,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>209</v>
+        <v>236</v>
       </c>
       <c r="C209">
         <v>510</v>
@@ -19806,7 +19994,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="C210">
         <v>1019</v>
@@ -19892,7 +20080,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="C211">
         <v>731</v>
@@ -19978,7 +20166,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>212</v>
+        <v>239</v>
       </c>
       <c r="C212">
         <v>555</v>
@@ -20064,7 +20252,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C213">
         <v>635</v>
@@ -20150,7 +20338,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>214</v>
+        <v>241</v>
       </c>
       <c r="C214">
         <v>998</v>
@@ -20236,7 +20424,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>215</v>
+        <v>242</v>
       </c>
       <c r="C215">
         <v>808</v>
@@ -20322,7 +20510,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>216</v>
+        <v>243</v>
       </c>
       <c r="C216">
         <v>597</v>
@@ -20408,7 +20596,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>217</v>
+        <v>244</v>
       </c>
       <c r="C217">
         <v>586</v>
@@ -20494,7 +20682,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="C218">
         <v>787</v>
@@ -20580,7 +20768,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>219</v>
+        <v>246</v>
       </c>
       <c r="C219">
         <v>766</v>
@@ -20666,7 +20854,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>220</v>
+        <v>247</v>
       </c>
       <c r="C220">
         <v>971</v>
@@ -20752,7 +20940,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="C221">
         <v>582</v>
@@ -20838,7 +21026,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>222</v>
+        <v>249</v>
       </c>
       <c r="C222">
         <v>812</v>
@@ -20924,7 +21112,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>223</v>
+        <v>250</v>
       </c>
       <c r="C223">
         <v>1068</v>
@@ -21010,7 +21198,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>224</v>
+        <v>251</v>
       </c>
       <c r="C224">
         <v>1135</v>
@@ -21096,7 +21284,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>225</v>
+        <v>252</v>
       </c>
       <c r="C225">
         <v>998</v>
@@ -21182,7 +21370,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>226</v>
+        <v>253</v>
       </c>
       <c r="C226">
         <v>971</v>
@@ -21268,7 +21456,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>227</v>
+        <v>254</v>
       </c>
       <c r="C227">
         <v>741</v>
@@ -21354,7 +21542,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="C228">
         <v>1041</v>
@@ -21440,7 +21628,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>229</v>
+        <v>256</v>
       </c>
       <c r="C229">
         <v>902</v>
@@ -21526,7 +21714,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>230</v>
+        <v>257</v>
       </c>
       <c r="C230">
         <v>1108</v>
@@ -21612,7 +21800,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>231</v>
+        <v>258</v>
       </c>
       <c r="C231">
         <v>1016</v>
@@ -21698,7 +21886,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>232</v>
+        <v>259</v>
       </c>
       <c r="C232">
         <v>699</v>
@@ -21784,7 +21972,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>233</v>
+        <v>260</v>
       </c>
       <c r="C233">
         <v>960</v>
@@ -21870,7 +22058,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>234</v>
+        <v>261</v>
       </c>
       <c r="C234">
         <v>716</v>
@@ -21956,7 +22144,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>235</v>
+        <v>262</v>
       </c>
       <c r="C235">
         <v>585</v>
@@ -22042,7 +22230,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="C236">
         <v>1195</v>
@@ -22128,7 +22316,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>237</v>
+        <v>264</v>
       </c>
       <c r="C237">
         <v>627</v>
@@ -22214,7 +22402,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>238</v>
+        <v>265</v>
       </c>
       <c r="C238">
         <v>636</v>
@@ -22300,7 +22488,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>239</v>
+        <v>266</v>
       </c>
       <c r="C239">
         <v>1060</v>
@@ -22386,7 +22574,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>240</v>
+        <v>267</v>
       </c>
       <c r="C240">
         <v>1069</v>
@@ -22472,7 +22660,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>241</v>
+        <v>268</v>
       </c>
       <c r="C241">
         <v>1126</v>
@@ -22558,7 +22746,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>242</v>
+        <v>269</v>
       </c>
       <c r="C242">
         <v>1097</v>
@@ -22644,7 +22832,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>243</v>
+        <v>270</v>
       </c>
       <c r="C243">
         <v>766</v>
@@ -22730,7 +22918,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>244</v>
+        <v>271</v>
       </c>
       <c r="C244">
         <v>708</v>
@@ -22816,7 +23004,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>245</v>
+        <v>272</v>
       </c>
       <c r="C245">
         <v>1165</v>
@@ -22902,7 +23090,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>246</v>
+        <v>273</v>
       </c>
       <c r="C246">
         <v>1024</v>
@@ -22988,7 +23176,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="C247">
         <v>823</v>
@@ -23074,7 +23262,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="C248">
         <v>401</v>
@@ -23160,7 +23348,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>249</v>
+        <v>276</v>
       </c>
       <c r="C249">
         <v>686</v>
@@ -23246,7 +23434,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>250</v>
+        <v>277</v>
       </c>
       <c r="C250">
         <v>780</v>
@@ -23332,7 +23520,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>251</v>
+        <v>278</v>
       </c>
       <c r="C251">
         <v>1078</v>
@@ -23418,7 +23606,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>252</v>
+        <v>279</v>
       </c>
       <c r="C252">
         <v>581</v>
@@ -23504,7 +23692,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>253</v>
+        <v>280</v>
       </c>
       <c r="C253">
         <v>845</v>
@@ -23590,7 +23778,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>254</v>
+        <v>281</v>
       </c>
       <c r="C254">
         <v>702</v>
@@ -23676,7 +23864,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>255</v>
+        <v>282</v>
       </c>
       <c r="C255">
         <v>655</v>
@@ -23762,7 +23950,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>256</v>
+        <v>283</v>
       </c>
       <c r="C256">
         <v>1095</v>
@@ -23848,7 +24036,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>257</v>
+        <v>284</v>
       </c>
       <c r="C257">
         <v>1039</v>
@@ -23934,7 +24122,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="C258">
         <v>768</v>
@@ -24020,7 +24208,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="C259">
         <v>520</v>
@@ -24106,7 +24294,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>260</v>
+        <v>287</v>
       </c>
       <c r="C260">
         <v>1112</v>
@@ -24192,7 +24380,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>261</v>
+        <v>288</v>
       </c>
       <c r="C261">
         <v>629</v>
@@ -24278,7 +24466,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="C262">
         <v>680</v>
@@ -24364,7 +24552,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="C263">
         <v>1146</v>
@@ -24450,7 +24638,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="C264">
         <v>1029</v>
@@ -24536,7 +24724,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="C265">
         <v>497</v>
@@ -24622,7 +24810,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="C266">
         <v>853</v>
@@ -24708,7 +24896,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="C267">
         <v>1168</v>
@@ -24794,7 +24982,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>268</v>
+        <v>295</v>
       </c>
       <c r="C268">
         <v>1165</v>
@@ -24880,7 +25068,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>269</v>
+        <v>296</v>
       </c>
       <c r="C269">
         <v>1120</v>
@@ -24966,7 +25154,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>270</v>
+        <v>297</v>
       </c>
       <c r="C270">
         <v>1057</v>
@@ -25052,7 +25240,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="C271">
         <v>1012</v>
@@ -25138,7 +25326,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>272</v>
+        <v>299</v>
       </c>
       <c r="C272">
         <v>768</v>
@@ -25224,7 +25412,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>273</v>
+        <v>300</v>
       </c>
       <c r="C273">
         <v>1001</v>
@@ -25310,7 +25498,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>274</v>
+        <v>301</v>
       </c>
       <c r="C274">
         <v>1190</v>
@@ -25396,7 +25584,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>275</v>
+        <v>302</v>
       </c>
       <c r="C275">
         <v>1039</v>
@@ -25482,7 +25670,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>276</v>
+        <v>303</v>
       </c>
       <c r="C276">
         <v>1096</v>
@@ -25568,7 +25756,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>277</v>
+        <v>304</v>
       </c>
       <c r="C277">
         <v>737</v>
@@ -25654,7 +25842,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="C278">
         <v>614</v>
@@ -25740,7 +25928,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>279</v>
+        <v>306</v>
       </c>
       <c r="C279">
         <v>721</v>
@@ -25826,7 +26014,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>280</v>
+        <v>307</v>
       </c>
       <c r="C280">
         <v>577</v>
@@ -25912,7 +26100,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>281</v>
+        <v>308</v>
       </c>
       <c r="C281">
         <v>635</v>
@@ -25998,7 +26186,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>282</v>
+        <v>309</v>
       </c>
       <c r="C282">
         <v>727</v>
@@ -26084,7 +26272,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>283</v>
+        <v>310</v>
       </c>
       <c r="C283">
         <v>1240</v>
@@ -26170,7 +26358,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>284</v>
+        <v>311</v>
       </c>
       <c r="C284">
         <v>1173</v>
@@ -26256,7 +26444,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>285</v>
+        <v>312</v>
       </c>
       <c r="C285">
         <v>736</v>
@@ -26342,7 +26530,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>286</v>
+        <v>313</v>
       </c>
       <c r="C286">
         <v>752</v>
@@ -26428,7 +26616,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>287</v>
+        <v>314</v>
       </c>
       <c r="C287">
         <v>617</v>
@@ -26514,7 +26702,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>288</v>
+        <v>315</v>
       </c>
       <c r="C288">
         <v>655</v>
@@ -26600,7 +26788,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>289</v>
+        <v>316</v>
       </c>
       <c r="C289">
         <v>681</v>
@@ -26686,7 +26874,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>290</v>
+        <v>317</v>
       </c>
       <c r="C290">
         <v>701</v>
@@ -26772,7 +26960,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>291</v>
+        <v>318</v>
       </c>
       <c r="C291">
         <v>953</v>
@@ -26858,7 +27046,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>292</v>
+        <v>319</v>
       </c>
       <c r="C292">
         <v>790</v>
@@ -26944,7 +27132,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>293</v>
+        <v>320</v>
       </c>
       <c r="C293">
         <v>875</v>
@@ -27030,7 +27218,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>294</v>
+        <v>321</v>
       </c>
       <c r="C294">
         <v>998</v>
@@ -27116,7 +27304,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>295</v>
+        <v>322</v>
       </c>
       <c r="C295">
         <v>946</v>
@@ -27202,7 +27390,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>296</v>
+        <v>323</v>
       </c>
       <c r="C296">
         <v>1158</v>
@@ -27288,7 +27476,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>297</v>
+        <v>324</v>
       </c>
       <c r="C297">
         <v>816</v>
@@ -27374,7 +27562,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>298</v>
+        <v>325</v>
       </c>
       <c r="C298">
         <v>1089</v>
@@ -27460,7 +27648,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>299</v>
+        <v>326</v>
       </c>
       <c r="C299">
         <v>1038</v>
@@ -27546,7 +27734,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>300</v>
+        <v>327</v>
       </c>
       <c r="C300">
         <v>714</v>
@@ -27632,7 +27820,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>301</v>
+        <v>328</v>
       </c>
       <c r="C301">
         <v>928</v>
@@ -27718,7 +27906,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>302</v>
+        <v>329</v>
       </c>
       <c r="C302">
         <v>697</v>
@@ -27804,7 +27992,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>303</v>
+        <v>330</v>
       </c>
       <c r="C303">
         <v>726</v>
@@ -27890,7 +28078,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>304</v>
+        <v>331</v>
       </c>
       <c r="C304">
         <v>1046</v>
@@ -27976,7 +28164,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>305</v>
+        <v>332</v>
       </c>
       <c r="C305">
         <v>1035</v>
@@ -28062,7 +28250,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>306</v>
+        <v>333</v>
       </c>
       <c r="C306">
         <v>833</v>
@@ -28148,7 +28336,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>307</v>
+        <v>334</v>
       </c>
       <c r="C307">
         <v>721</v>
@@ -28234,7 +28422,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>308</v>
+        <v>335</v>
       </c>
       <c r="C308">
         <v>657</v>
@@ -28320,7 +28508,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>309</v>
+        <v>336</v>
       </c>
       <c r="C309">
         <v>627</v>
@@ -28406,7 +28594,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>310</v>
+        <v>337</v>
       </c>
       <c r="C310">
         <v>1119</v>
@@ -28492,7 +28680,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>311</v>
+        <v>338</v>
       </c>
       <c r="C311">
         <v>867</v>
@@ -28578,7 +28766,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>312</v>
+        <v>339</v>
       </c>
       <c r="C312">
         <v>1011</v>
@@ -28664,7 +28852,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>313</v>
+        <v>340</v>
       </c>
       <c r="C313">
         <v>684</v>
@@ -28750,7 +28938,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>314</v>
+        <v>341</v>
       </c>
       <c r="C314">
         <v>764</v>
@@ -28836,7 +29024,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>315</v>
+        <v>342</v>
       </c>
       <c r="C315">
         <v>1173</v>
@@ -28922,7 +29110,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>316</v>
+        <v>343</v>
       </c>
       <c r="C316">
         <v>709</v>
@@ -29008,7 +29196,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>317</v>
+        <v>344</v>
       </c>
       <c r="C317">
         <v>693</v>
@@ -29094,7 +29282,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>318</v>
+        <v>345</v>
       </c>
       <c r="C318">
         <v>669</v>
@@ -29180,7 +29368,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>319</v>
+        <v>346</v>
       </c>
       <c r="C319">
         <v>603</v>
@@ -29266,7 +29454,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>320</v>
+        <v>347</v>
       </c>
       <c r="C320">
         <v>821</v>
@@ -29352,7 +29540,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>321</v>
+        <v>348</v>
       </c>
       <c r="C321">
         <v>732</v>
@@ -29438,7 +29626,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>322</v>
+        <v>349</v>
       </c>
       <c r="C322">
         <v>844</v>
@@ -29524,7 +29712,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>323</v>
+        <v>350</v>
       </c>
       <c r="C323">
         <v>727</v>
@@ -29610,7 +29798,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>324</v>
+        <v>351</v>
       </c>
       <c r="C324">
         <v>692</v>
@@ -29696,7 +29884,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>325</v>
+        <v>352</v>
       </c>
       <c r="C325">
         <v>764</v>
@@ -29782,7 +29970,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>326</v>
+        <v>353</v>
       </c>
       <c r="C326">
         <v>690</v>
@@ -29868,7 +30056,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>327</v>
+        <v>354</v>
       </c>
       <c r="C327">
         <v>674</v>
@@ -29954,7 +30142,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>328</v>
+        <v>355</v>
       </c>
       <c r="C328">
         <v>753</v>
@@ -30040,7 +30228,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>329</v>
+        <v>356</v>
       </c>
       <c r="C329">
         <v>897</v>
@@ -30126,7 +30314,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>330</v>
+        <v>357</v>
       </c>
       <c r="C330">
         <v>746</v>
@@ -30212,7 +30400,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>331</v>
+        <v>358</v>
       </c>
       <c r="C331">
         <v>814</v>
@@ -30298,7 +30486,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>332</v>
+        <v>359</v>
       </c>
       <c r="C332">
         <v>1052</v>
@@ -30384,7 +30572,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>333</v>
+        <v>360</v>
       </c>
       <c r="C333">
         <v>662</v>
@@ -30470,7 +30658,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>334</v>
+        <v>361</v>
       </c>
       <c r="C334">
         <v>756</v>
@@ -30556,7 +30744,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>335</v>
+        <v>362</v>
       </c>
       <c r="C335">
         <v>790</v>
@@ -30642,7 +30830,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>336</v>
+        <v>363</v>
       </c>
       <c r="C336">
         <v>745</v>
@@ -30728,7 +30916,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>337</v>
+        <v>364</v>
       </c>
       <c r="C337">
         <v>668</v>
@@ -30814,7 +31002,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>338</v>
+        <v>365</v>
       </c>
       <c r="C338">
         <v>768</v>
@@ -30900,7 +31088,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>339</v>
+        <v>366</v>
       </c>
       <c r="C339">
         <v>1209</v>
@@ -30986,7 +31174,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>340</v>
+        <v>367</v>
       </c>
       <c r="C340">
         <v>978</v>
@@ -31072,7 +31260,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>341</v>
+        <v>368</v>
       </c>
       <c r="C341">
         <v>1199</v>
@@ -31158,7 +31346,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>342</v>
+        <v>369</v>
       </c>
       <c r="C342">
         <v>1088</v>
@@ -31244,7 +31432,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>343</v>
+        <v>370</v>
       </c>
       <c r="C343">
         <v>1059</v>
@@ -31330,7 +31518,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>344</v>
+        <v>371</v>
       </c>
       <c r="C344">
         <v>1012</v>
@@ -31416,7 +31604,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>345</v>
+        <v>372</v>
       </c>
       <c r="C345">
         <v>1026</v>
@@ -31502,7 +31690,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>346</v>
+        <v>373</v>
       </c>
       <c r="C346">
         <v>768</v>
@@ -31588,7 +31776,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>347</v>
+        <v>374</v>
       </c>
       <c r="C347">
         <v>846</v>
@@ -31674,7 +31862,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>348</v>
+        <v>375</v>
       </c>
       <c r="C348">
         <v>928</v>
@@ -31760,7 +31948,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>349</v>
+        <v>376</v>
       </c>
       <c r="C349">
         <v>1154</v>
@@ -31846,7 +32034,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>350</v>
+        <v>377</v>
       </c>
       <c r="C350">
         <v>789</v>
@@ -31932,7 +32120,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>351</v>
+        <v>378</v>
       </c>
       <c r="C351">
         <v>724</v>
@@ -32018,7 +32206,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>352</v>
+        <v>379</v>
       </c>
       <c r="C352">
         <v>830</v>
@@ -32104,7 +32292,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>353</v>
+        <v>380</v>
       </c>
       <c r="C353">
         <v>874</v>
@@ -32190,7 +32378,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>354</v>
+        <v>381</v>
       </c>
       <c r="C354">
         <v>611</v>
@@ -32276,7 +32464,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>355</v>
+        <v>382</v>
       </c>
       <c r="C355">
         <v>974</v>
@@ -32362,7 +32550,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>356</v>
+        <v>383</v>
       </c>
       <c r="C356">
         <v>750</v>
@@ -32448,7 +32636,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>357</v>
+        <v>384</v>
       </c>
       <c r="C357">
         <v>706</v>
@@ -32534,7 +32722,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>358</v>
+        <v>385</v>
       </c>
       <c r="C358">
         <v>708</v>
@@ -32620,7 +32808,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>359</v>
+        <v>386</v>
       </c>
       <c r="C359">
         <v>767</v>
@@ -32706,7 +32894,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>360</v>
+        <v>387</v>
       </c>
       <c r="C360">
         <v>827</v>
@@ -32792,7 +32980,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>361</v>
+        <v>388</v>
       </c>
       <c r="C361">
         <v>768</v>
@@ -32878,7 +33066,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>362</v>
+        <v>389</v>
       </c>
       <c r="C362">
         <v>758</v>
@@ -32964,7 +33152,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>363</v>
+        <v>390</v>
       </c>
       <c r="C363">
         <v>843</v>
@@ -33050,7 +33238,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>364</v>
+        <v>391</v>
       </c>
       <c r="C364">
         <v>647</v>
@@ -33136,7 +33324,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>365</v>
+        <v>392</v>
       </c>
       <c r="C365">
         <v>786</v>
@@ -33222,7 +33410,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>366</v>
+        <v>393</v>
       </c>
       <c r="C366">
         <v>546</v>
@@ -33308,7 +33496,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>367</v>
+        <v>394</v>
       </c>
       <c r="C367">
         <v>795</v>
@@ -33394,7 +33582,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>368</v>
+        <v>395</v>
       </c>
       <c r="C368">
         <v>907</v>
@@ -33480,7 +33668,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="C369">
         <v>696</v>
@@ -33566,7 +33754,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>370</v>
+        <v>397</v>
       </c>
       <c r="C370">
         <v>411</v>
@@ -33652,7 +33840,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>371</v>
+        <v>398</v>
       </c>
       <c r="C371">
         <v>807</v>
@@ -33738,7 +33926,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="C372">
         <v>1205</v>
@@ -33824,7 +34012,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>373</v>
+        <v>400</v>
       </c>
       <c r="C373">
         <v>714</v>
@@ -33910,7 +34098,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>374</v>
+        <v>401</v>
       </c>
       <c r="C374">
         <v>605</v>
@@ -33996,7 +34184,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>375</v>
+        <v>402</v>
       </c>
       <c r="C375">
         <v>1020</v>
@@ -34082,7 +34270,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>376</v>
+        <v>403</v>
       </c>
       <c r="C376">
         <v>1037</v>
@@ -34168,7 +34356,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>377</v>
+        <v>404</v>
       </c>
       <c r="C377">
         <v>974</v>
@@ -34254,7 +34442,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>378</v>
+        <v>405</v>
       </c>
       <c r="C378">
         <v>1120</v>
@@ -34340,7 +34528,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>379</v>
+        <v>406</v>
       </c>
       <c r="C379">
         <v>727</v>
@@ -34426,7 +34614,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>380</v>
+        <v>407</v>
       </c>
       <c r="C380">
         <v>577</v>
@@ -34512,7 +34700,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="C381">
         <v>1098</v>
@@ -34598,7 +34786,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>382</v>
+        <v>409</v>
       </c>
       <c r="C382">
         <v>967</v>
@@ -34684,7 +34872,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>383</v>
+        <v>410</v>
       </c>
       <c r="C383">
         <v>1173</v>
@@ -34770,7 +34958,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="C384">
         <v>753</v>
@@ -34856,7 +35044,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>385</v>
+        <v>412</v>
       </c>
       <c r="C385">
         <v>1058</v>
@@ -34942,7 +35130,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>386</v>
+        <v>413</v>
       </c>
       <c r="C386">
         <v>1039</v>
@@ -35028,7 +35216,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>387</v>
+        <v>414</v>
       </c>
       <c r="C387">
         <v>1180</v>
@@ -35114,7 +35302,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>388</v>
+        <v>415</v>
       </c>
       <c r="C388">
         <v>1100</v>
@@ -35200,7 +35388,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>389</v>
+        <v>416</v>
       </c>
       <c r="C389">
         <v>937</v>
@@ -35286,7 +35474,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>390</v>
+        <v>417</v>
       </c>
       <c r="C390">
         <v>906</v>
@@ -35372,7 +35560,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>391</v>
+        <v>418</v>
       </c>
       <c r="C391">
         <v>960</v>
@@ -35458,7 +35646,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>392</v>
+        <v>419</v>
       </c>
       <c r="C392">
         <v>739</v>
@@ -35544,7 +35732,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>393</v>
+        <v>420</v>
       </c>
       <c r="C393">
         <v>671</v>
@@ -35630,7 +35818,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>394</v>
+        <v>421</v>
       </c>
       <c r="C394">
         <v>1058</v>
@@ -35716,7 +35904,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>395</v>
+        <v>422</v>
       </c>
       <c r="C395">
         <v>1119</v>
@@ -35802,7 +35990,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>396</v>
+        <v>423</v>
       </c>
       <c r="C396">
         <v>685</v>
@@ -35888,7 +36076,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>397</v>
+        <v>424</v>
       </c>
       <c r="C397">
         <v>638</v>
@@ -35974,7 +36162,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>398</v>
+        <v>425</v>
       </c>
       <c r="C398">
         <v>1018</v>
@@ -36060,7 +36248,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>399</v>
+        <v>426</v>
       </c>
       <c r="C399">
         <v>709</v>
@@ -36146,7 +36334,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>400</v>
+        <v>427</v>
       </c>
       <c r="C400">
         <v>663</v>
@@ -36232,7 +36420,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>401</v>
+        <v>428</v>
       </c>
       <c r="C401">
         <v>1076</v>
@@ -36318,7 +36506,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>402</v>
+        <v>429</v>
       </c>
       <c r="C402">
         <v>1194</v>
@@ -36404,7 +36592,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>403</v>
+        <v>430</v>
       </c>
       <c r="C403">
         <v>1024</v>
@@ -36490,7 +36678,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>404</v>
+        <v>431</v>
       </c>
       <c r="C404">
         <v>722</v>
@@ -36576,7 +36764,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>405</v>
+        <v>432</v>
       </c>
       <c r="C405">
         <v>754</v>
@@ -36662,7 +36850,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>406</v>
+        <v>433</v>
       </c>
       <c r="C406">
         <v>864</v>
@@ -36748,7 +36936,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>407</v>
+        <v>434</v>
       </c>
       <c r="C407">
         <v>980</v>
@@ -36834,7 +37022,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>408</v>
+        <v>435</v>
       </c>
       <c r="C408">
         <v>653</v>
@@ -36920,7 +37108,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>409</v>
+        <v>436</v>
       </c>
       <c r="C409">
         <v>713</v>
@@ -37006,7 +37194,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>410</v>
+        <v>437</v>
       </c>
       <c r="C410">
         <v>1056</v>
@@ -37092,7 +37280,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>411</v>
+        <v>438</v>
       </c>
       <c r="C411">
         <v>653</v>
@@ -37178,7 +37366,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>412</v>
+        <v>439</v>
       </c>
       <c r="C412">
         <v>1189</v>
@@ -37264,7 +37452,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>413</v>
+        <v>440</v>
       </c>
       <c r="C413">
         <v>900</v>
@@ -37350,7 +37538,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>414</v>
+        <v>441</v>
       </c>
       <c r="C414">
         <v>992</v>
@@ -37436,7 +37624,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>415</v>
+        <v>442</v>
       </c>
       <c r="C415">
         <v>257</v>
@@ -37522,7 +37710,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>416</v>
+        <v>443</v>
       </c>
       <c r="C416">
         <v>778</v>
@@ -37608,7 +37796,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>417</v>
+        <v>444</v>
       </c>
       <c r="C417">
         <v>878</v>
@@ -37694,7 +37882,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>418</v>
+        <v>445</v>
       </c>
       <c r="C418">
         <v>1043</v>
@@ -37780,7 +37968,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>419</v>
+        <v>446</v>
       </c>
       <c r="C419">
         <v>947</v>
@@ -37866,7 +38054,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>420</v>
+        <v>447</v>
       </c>
       <c r="C420">
         <v>734</v>
@@ -37952,7 +38140,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>421</v>
+        <v>448</v>
       </c>
       <c r="C421">
         <v>1161</v>
@@ -38038,7 +38226,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>422</v>
+        <v>449</v>
       </c>
       <c r="C422">
         <v>884</v>
@@ -38124,7 +38312,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="C423">
         <v>741</v>
@@ -38210,7 +38398,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>424</v>
+        <v>451</v>
       </c>
       <c r="C424">
         <v>850</v>
@@ -38296,7 +38484,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>425</v>
+        <v>452</v>
       </c>
       <c r="C425">
         <v>677</v>
@@ -38382,7 +38570,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="C426">
         <v>634</v>
@@ -38468,7 +38656,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>427</v>
+        <v>454</v>
       </c>
       <c r="C427">
         <v>836</v>
@@ -38554,7 +38742,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>428</v>
+        <v>455</v>
       </c>
       <c r="C428">
         <v>676</v>
@@ -38640,7 +38828,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>429</v>
+        <v>456</v>
       </c>
       <c r="C429">
         <v>661</v>
@@ -38726,7 +38914,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>430</v>
+        <v>457</v>
       </c>
       <c r="C430">
         <v>848</v>
@@ -38812,7 +39000,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>431</v>
+        <v>458</v>
       </c>
       <c r="C431">
         <v>843</v>
@@ -38898,7 +39086,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="s">
-        <v>432</v>
+        <v>459</v>
       </c>
       <c r="C432">
         <v>773</v>
@@ -38984,7 +39172,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="s">
-        <v>433</v>
+        <v>460</v>
       </c>
       <c r="C433">
         <v>823</v>
@@ -39070,7 +39258,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="s">
-        <v>434</v>
+        <v>461</v>
       </c>
       <c r="C434">
         <v>722</v>
@@ -39156,7 +39344,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="s">
-        <v>435</v>
+        <v>462</v>
       </c>
       <c r="C435">
         <v>751</v>
@@ -39242,7 +39430,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="s">
-        <v>436</v>
+        <v>463</v>
       </c>
       <c r="C436">
         <v>617</v>
@@ -39328,7 +39516,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="s">
-        <v>437</v>
+        <v>464</v>
       </c>
       <c r="C437">
         <v>964</v>
@@ -39414,7 +39602,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="s">
-        <v>438</v>
+        <v>465</v>
       </c>
       <c r="C438">
         <v>675</v>
@@ -39500,7 +39688,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="s">
-        <v>439</v>
+        <v>466</v>
       </c>
       <c r="C439">
         <v>592</v>
@@ -39586,7 +39774,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="s">
-        <v>440</v>
+        <v>467</v>
       </c>
       <c r="C440">
         <v>665</v>
@@ -39672,7 +39860,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="s">
-        <v>441</v>
+        <v>468</v>
       </c>
       <c r="C441">
         <v>568</v>
@@ -39758,7 +39946,7 @@
         <v>440</v>
       </c>
       <c r="B442" t="s">
-        <v>442</v>
+        <v>469</v>
       </c>
       <c r="C442">
         <v>830</v>
@@ -39844,7 +40032,7 @@
         <v>441</v>
       </c>
       <c r="B443" t="s">
-        <v>443</v>
+        <v>470</v>
       </c>
       <c r="C443">
         <v>689</v>
@@ -39930,7 +40118,7 @@
         <v>442</v>
       </c>
       <c r="B444" t="s">
-        <v>444</v>
+        <v>471</v>
       </c>
       <c r="C444">
         <v>746</v>
@@ -40016,7 +40204,7 @@
         <v>443</v>
       </c>
       <c r="B445" t="s">
-        <v>445</v>
+        <v>472</v>
       </c>
       <c r="C445">
         <v>786</v>
@@ -40102,7 +40290,7 @@
         <v>444</v>
       </c>
       <c r="B446" t="s">
-        <v>446</v>
+        <v>473</v>
       </c>
       <c r="C446">
         <v>766</v>
@@ -40188,7 +40376,7 @@
         <v>445</v>
       </c>
       <c r="B447" t="s">
-        <v>447</v>
+        <v>474</v>
       </c>
       <c r="C447">
         <v>979</v>
@@ -40274,7 +40462,7 @@
         <v>446</v>
       </c>
       <c r="B448" t="s">
-        <v>448</v>
+        <v>475</v>
       </c>
       <c r="C448">
         <v>929</v>
@@ -40360,7 +40548,7 @@
         <v>447</v>
       </c>
       <c r="B449" t="s">
-        <v>449</v>
+        <v>476</v>
       </c>
       <c r="C449">
         <v>853</v>
@@ -40446,7 +40634,7 @@
         <v>448</v>
       </c>
       <c r="B450" t="s">
-        <v>450</v>
+        <v>477</v>
       </c>
       <c r="C450">
         <v>750</v>
@@ -40532,7 +40720,7 @@
         <v>449</v>
       </c>
       <c r="B451" t="s">
-        <v>451</v>
+        <v>478</v>
       </c>
       <c r="C451">
         <v>808</v>
@@ -40618,7 +40806,7 @@
         <v>450</v>
       </c>
       <c r="B452" t="s">
-        <v>452</v>
+        <v>479</v>
       </c>
       <c r="C452">
         <v>503</v>
@@ -40704,7 +40892,7 @@
         <v>451</v>
       </c>
       <c r="B453" t="s">
-        <v>453</v>
+        <v>480</v>
       </c>
       <c r="C453">
         <v>421</v>
@@ -40790,7 +40978,7 @@
         <v>452</v>
       </c>
       <c r="B454" t="s">
-        <v>454</v>
+        <v>481</v>
       </c>
       <c r="C454">
         <v>657</v>
@@ -40876,7 +41064,7 @@
         <v>453</v>
       </c>
       <c r="B455" t="s">
-        <v>455</v>
+        <v>482</v>
       </c>
       <c r="C455">
         <v>630</v>
@@ -40962,7 +41150,7 @@
         <v>454</v>
       </c>
       <c r="B456" t="s">
-        <v>456</v>
+        <v>483</v>
       </c>
       <c r="C456">
         <v>1045</v>
@@ -41048,7 +41236,7 @@
         <v>455</v>
       </c>
       <c r="B457" t="s">
-        <v>457</v>
+        <v>484</v>
       </c>
       <c r="C457">
         <v>635</v>
@@ -41134,7 +41322,7 @@
         <v>456</v>
       </c>
       <c r="B458" t="s">
-        <v>458</v>
+        <v>485</v>
       </c>
       <c r="C458">
         <v>616</v>
@@ -41220,7 +41408,7 @@
         <v>457</v>
       </c>
       <c r="B459" t="s">
-        <v>459</v>
+        <v>486</v>
       </c>
       <c r="C459">
         <v>738</v>
@@ -41306,7 +41494,7 @@
         <v>458</v>
       </c>
       <c r="B460" t="s">
-        <v>460</v>
+        <v>487</v>
       </c>
       <c r="C460">
         <v>689</v>
@@ -41392,7 +41580,7 @@
         <v>459</v>
       </c>
       <c r="B461" t="s">
-        <v>461</v>
+        <v>488</v>
       </c>
       <c r="C461">
         <v>916</v>
@@ -41478,7 +41666,7 @@
         <v>460</v>
       </c>
       <c r="B462" t="s">
-        <v>462</v>
+        <v>489</v>
       </c>
       <c r="C462">
         <v>892</v>
@@ -41564,7 +41752,7 @@
         <v>461</v>
       </c>
       <c r="B463" t="s">
-        <v>463</v>
+        <v>490</v>
       </c>
       <c r="C463">
         <v>659</v>
@@ -41650,7 +41838,7 @@
         <v>462</v>
       </c>
       <c r="B464" t="s">
-        <v>464</v>
+        <v>491</v>
       </c>
       <c r="C464">
         <v>650</v>
@@ -41736,7 +41924,7 @@
         <v>463</v>
       </c>
       <c r="B465" t="s">
-        <v>465</v>
+        <v>492</v>
       </c>
       <c r="C465">
         <v>666</v>
@@ -41822,7 +42010,7 @@
         <v>464</v>
       </c>
       <c r="B466" t="s">
-        <v>466</v>
+        <v>493</v>
       </c>
       <c r="C466">
         <v>776</v>
@@ -41908,7 +42096,7 @@
         <v>465</v>
       </c>
       <c r="B467" t="s">
-        <v>467</v>
+        <v>494</v>
       </c>
       <c r="C467">
         <v>879</v>
@@ -41994,7 +42182,7 @@
         <v>466</v>
       </c>
       <c r="B468" t="s">
-        <v>468</v>
+        <v>495</v>
       </c>
       <c r="C468">
         <v>1001</v>
@@ -42080,7 +42268,7 @@
         <v>467</v>
       </c>
       <c r="B469" t="s">
-        <v>469</v>
+        <v>496</v>
       </c>
       <c r="C469">
         <v>1055</v>
@@ -42166,7 +42354,7 @@
         <v>468</v>
       </c>
       <c r="B470" t="s">
-        <v>470</v>
+        <v>497</v>
       </c>
       <c r="C470">
         <v>624</v>
@@ -42252,7 +42440,7 @@
         <v>469</v>
       </c>
       <c r="B471" t="s">
-        <v>471</v>
+        <v>498</v>
       </c>
       <c r="C471">
         <v>1179</v>
@@ -42338,7 +42526,7 @@
         <v>470</v>
       </c>
       <c r="B472" t="s">
-        <v>472</v>
+        <v>499</v>
       </c>
       <c r="C472">
         <v>1005</v>
@@ -42424,7 +42612,7 @@
         <v>471</v>
       </c>
       <c r="B473" t="s">
-        <v>473</v>
+        <v>500</v>
       </c>
       <c r="C473">
         <v>952</v>
@@ -42510,7 +42698,7 @@
         <v>472</v>
       </c>
       <c r="B474" t="s">
-        <v>474</v>
+        <v>501</v>
       </c>
       <c r="C474">
         <v>692</v>
@@ -42596,7 +42784,7 @@
         <v>473</v>
       </c>
       <c r="B475" t="s">
-        <v>475</v>
+        <v>502</v>
       </c>
       <c r="C475">
         <v>581</v>
@@ -42682,7 +42870,7 @@
         <v>474</v>
       </c>
       <c r="B476" t="s">
-        <v>476</v>
+        <v>503</v>
       </c>
       <c r="C476">
         <v>674</v>
@@ -42768,7 +42956,7 @@
         <v>475</v>
       </c>
       <c r="B477" t="s">
-        <v>477</v>
+        <v>504</v>
       </c>
       <c r="C477">
         <v>730</v>
@@ -42854,7 +43042,7 @@
         <v>476</v>
       </c>
       <c r="B478" t="s">
-        <v>478</v>
+        <v>505</v>
       </c>
       <c r="C478">
         <v>1206</v>
@@ -42940,7 +43128,7 @@
         <v>477</v>
       </c>
       <c r="B479" t="s">
-        <v>479</v>
+        <v>506</v>
       </c>
       <c r="C479">
         <v>961</v>
@@ -43026,7 +43214,7 @@
         <v>478</v>
       </c>
       <c r="B480" t="s">
-        <v>480</v>
+        <v>507</v>
       </c>
       <c r="C480">
         <v>1165</v>
@@ -43112,7 +43300,7 @@
         <v>479</v>
       </c>
       <c r="B481" t="s">
-        <v>481</v>
+        <v>508</v>
       </c>
       <c r="C481">
         <v>982</v>
@@ -43198,7 +43386,7 @@
         <v>480</v>
       </c>
       <c r="B482" t="s">
-        <v>482</v>
+        <v>509</v>
       </c>
       <c r="C482">
         <v>768</v>
@@ -43284,7 +43472,7 @@
         <v>481</v>
       </c>
       <c r="B483" t="s">
-        <v>483</v>
+        <v>510</v>
       </c>
       <c r="C483">
         <v>755</v>
@@ -43370,7 +43558,7 @@
         <v>482</v>
       </c>
       <c r="B484" t="s">
-        <v>484</v>
+        <v>511</v>
       </c>
       <c r="C484">
         <v>558</v>
@@ -43456,7 +43644,7 @@
         <v>483</v>
       </c>
       <c r="B485" t="s">
-        <v>485</v>
+        <v>512</v>
       </c>
       <c r="C485">
         <v>1112</v>
@@ -43542,7 +43730,7 @@
         <v>484</v>
       </c>
       <c r="B486" t="s">
-        <v>486</v>
+        <v>513</v>
       </c>
       <c r="C486">
         <v>1195</v>
@@ -43628,7 +43816,7 @@
         <v>485</v>
       </c>
       <c r="B487" t="s">
-        <v>487</v>
+        <v>514</v>
       </c>
       <c r="C487">
         <v>1082</v>
@@ -43714,7 +43902,7 @@
         <v>486</v>
       </c>
       <c r="B488" t="s">
-        <v>488</v>
+        <v>515</v>
       </c>
       <c r="C488">
         <v>662</v>
@@ -43800,7 +43988,7 @@
         <v>487</v>
       </c>
       <c r="B489" t="s">
-        <v>489</v>
+        <v>516</v>
       </c>
       <c r="C489">
         <v>862</v>
@@ -43886,7 +44074,7 @@
         <v>488</v>
       </c>
       <c r="B490" t="s">
-        <v>490</v>
+        <v>517</v>
       </c>
       <c r="C490">
         <v>865</v>
@@ -43972,7 +44160,7 @@
         <v>489</v>
       </c>
       <c r="B491" t="s">
-        <v>491</v>
+        <v>518</v>
       </c>
       <c r="C491">
         <v>940</v>
@@ -44058,7 +44246,7 @@
         <v>490</v>
       </c>
       <c r="B492" t="s">
-        <v>492</v>
+        <v>519</v>
       </c>
       <c r="C492">
         <v>900</v>
@@ -44144,7 +44332,7 @@
         <v>491</v>
       </c>
       <c r="B493" t="s">
-        <v>493</v>
+        <v>520</v>
       </c>
       <c r="C493">
         <v>664</v>
@@ -44230,7 +44418,7 @@
         <v>492</v>
       </c>
       <c r="B494" t="s">
-        <v>494</v>
+        <v>521</v>
       </c>
       <c r="C494">
         <v>588</v>
